--- a/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans le salon. Son nez chatouille. Maman est près du canapé. Maman tend un mouchoir. Hugo prend un mouchoir. Il se mouche. Atchoum, tout doux. Le nez est plus libre. Hugo va jeter le mouchoir. Il le met dans la poubelle. Maman dit : mouchoir, puis poubelle. Hugo va au lavabo. Il se lave les mains. Il revient. Maman sourit. Hugo respire mieux.</t>
+          <t>Hugo est dans le salon. Son nez chatouille. Maman est près du canapé. Maman tend un mouchoir. Hugo prend un mouchoir. Il se mouche. Atchoum, tout doux. Le nez est plus libre. Hugo va jeter le mouchoir. Il le met dans la poubelle. Mouchoir, puis poubelle. Hugo va au lavabo. Il se lave les mains. Il revient. Maman sourit. Hugo respire mieux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est dans le salon. Son nez chatouille. Maman est près du canapé. Maman tend un mouchoir. Hugo prend un mouchoir. Il se mouche. Atchoum, tout doux. Le nez est plus libre. Hugo va jeter le mouchoir. Il le met dans la poubelle.
+maman|Mouchoir, puis poubelle.
+narrateur|Hugo va au lavabo. Il se lave les mains. Il revient. Maman sourit. Hugo respire mieux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo se mouche. Que prend-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo s'assoit près de maman. Son nez est calme. Il dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Hugo va au lavabo. Il se lave les mains. Il revient. Maman sourit. Hugo respire mieux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Hugo se mouche. Que prend-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Hugo a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Hugo s'assoit près de maman. Son nez est calme. Il dit merci.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le mouchoir de Hugo</t>
+          <t>Le mouchoir de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La pluie tape la vitre. Les cubes attendent. Le nez de Nino chatouille. Mouchoir, puis poubelle.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo est dans le salon. Son nez chatouille. Maman est près du canapé. Maman tend un mouchoir. Hugo prend un mouchoir. Il se mouche. Atchoum, tout doux. Le nez est plus libre. Hugo va jeter le mouchoir. Il le met dans la poubelle. Mouchoir, puis poubelle. Hugo va au lavabo. Il se lave les mains. Il revient. Maman sourit. Hugo respire mieux.</t>
+          <t>La pluie tape la vitre. Ça fait tic, tic, tic. Le radiateur est chaud. Le canapé a une couverture bleue. Une tour de cubes attend sur le tapis. Un cube rouge. Un cube vert. Nino, tu entends la pluie ? Oui. Tic, tic. Le radiateur est chaud. Mes mains aussi. En ce moment, Nino est au salon. Il touche un cube rouge. Son nez chatouille. Atchoum. Ton nez chatouille ? Oui, maman. Maman ouvre la boîte près du canapé. Maman tend un mouchoir. Prends un mouchoir. Nino prend un mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum, tout doux. Le nez est plus libre. Je respire. Mouchoir, puis poubelle. Nino va vers la poubelle. Il met le mouchoir dedans. La poubelle fait un petit bruit. Bravo. Tu as jeté le mouchoir. C'est du bon travail. Nino va au lavabo. Il se lave les mains. L'eau est tiède. Tu as fini de laver tes mains ? Oui, maman. Nino revient près des cubes. La tour attend encore. On pose le cube rouge ? Oui. Tout doux. Le cube rouge tient. La pluie tape encore. Tic, tic. Ton nez est calme, maintenant. Je respire mieux. Parce que tu as pris un mouchoir. Puis la poubelle. Mouchoir, poubelle. Oui. Bravo, Nino. Nino pose le cube vert. La tour est plus haute. Elle tient, la tour. Le rouge, puis le vert. Tu as les mains propres. Le radiateur ronronne tout bas. La couverture bleue glisse un peu. On la remet ? Oui. Elle est douce. Nino tire la couverture. Le canapé est chaud près du radiateur. La pluie continue. Tic, tic, tic. Et ton nez ? Calme. Mouchoir, poubelle. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,78 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est dans le salon. Son nez chatouille. Maman est près du canapé. Maman tend un mouchoir. Hugo prend un mouchoir. Il se mouche. Atchoum, tout doux. Le nez est plus libre. Hugo va jeter le mouchoir. Il le met dans la poubelle.
+          <t>narrateur|La pluie tape la vitre.
+narrateur|Ça fait tic, tic, tic.
+narrateur|Le radiateur est chaud.
+narrateur|Le canapé a une couverture bleue.
+narrateur|Une tour de cubes attend sur le tapis.
+narrateur|Un cube rouge. Un cube vert.
+maman|Nino, tu entends la pluie ?
+enfant-m|Oui. Tic, tic.
+maman|Le radiateur est chaud.
+enfant-m|Mes mains aussi.
+narrateur|En ce moment, Nino est au salon.
+narrateur|Il touche un cube rouge.
+narrateur|Son nez chatouille.
+enfant-m|Atchoum.
+maman|Ton nez chatouille ?
+enfant-m|Oui, maman.
+narrateur|Maman ouvre la boîte près du canapé.
+narrateur|Maman tend un mouchoir.
+maman|Prends un mouchoir.
+narrateur|Nino prend un mouchoir.
+narrateur|Le papier est doux.
+narrateur|Il se mouche, tout doux.
+enfant-m|Atchoum, tout doux.
+maman|Le nez est plus libre.
+enfant-m|Je respire.
 maman|Mouchoir, puis poubelle.
-narrateur|Hugo va au lavabo. Il se lave les mains. Il revient. Maman sourit. Hugo respire mieux.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Nino va vers la poubelle.
+narrateur|Il met le mouchoir dedans.
+narrateur|La poubelle fait un petit bruit.
+maman|Bravo. Tu as jeté le mouchoir.
+maman|C'est du bon travail.
+narrateur|Nino va au lavabo.
+narrateur|Il se lave les mains.
+narrateur|L'eau est tiède.
+maman|Tu as fini de laver tes mains ?
+enfant-m|Oui, maman.
+narrateur|Nino revient près des cubes.
+narrateur|La tour attend encore.
+maman|On pose le cube rouge ?
+enfant-m|Oui. Tout doux.
+narrateur|Le cube rouge tient.
+narrateur|La pluie tape encore.
+enfant-m|Tic, tic.
+maman|Ton nez est calme, maintenant.
+enfant-m|Je respire mieux.
+maman|Parce que tu as pris un mouchoir.
+maman|Puis la poubelle.
+enfant-m|Mouchoir, poubelle.
+maman|Oui. Bravo, Nino.
+narrateur|Nino pose le cube vert.
+narrateur|La tour est plus haute.
+maman|Elle tient, la tour.
+enfant-m|Le rouge, puis le vert.
+maman|Tu as les mains propres.
+narrateur|Le radiateur ronronne tout bas.
+narrateur|La couverture bleue glisse un peu.
+maman|On la remet ?
+enfant-m|Oui. Elle est douce.
+narrateur|Nino tire la couverture.
+narrateur|Le canapé est chaud près du radiateur.
+maman|La pluie continue.
+enfant-m|Tic, tic, tic.
+maman|Et ton nez ?
+enfant-m|Calme. Mouchoir, poubelle.
+maman|Bravo. C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie_fenetre</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hugo se mouche. Que prend-il ?</t>
+          <t>Nino se mouche. Que prend-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,10 +1576,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hugo se mouche. Que prend-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino se mouche.
+narrateur|Que prend-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,7 +1604,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
+          <t>Nino a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Bravo. C'est du bon travail. La tour de cubes tient encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,10 +1748,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino a pris un mouchoir.
+narrateur|Il s'est mouché.
+narrateur|Il a jeté le mouchoir à la poubelle.
+maman|Tu as pris un mouchoir ?
+enfant-m|Oui. Puis poubelle.
+maman|Bravo. C'est du bon travail.
+narrateur|La tour de cubes tient encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'assoit près de maman. Son nez est calme. Il dit merci.</t>
+          <t>Nino s'assoit près de maman. La couverture bleue est douce. Merci, maman. Ton nez est calme. La pluie tape plus loin. Tic, tout doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,10 +1917,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugo s'assoit près de maman. Son nez est calme. Il dit merci.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino s'assoit près de maman.
+narrateur|La couverture bleue est douce.
+enfant-m|Merci, maman.
+maman|Ton nez est calme.
+narrateur|La pluie tape plus loin.
+enfant-m|Tic, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1862,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Mouchoir, puis poubelle. Bravo, Nino. Le cube rouge reste en haut. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,10 +2089,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Mouchoir, puis poubelle.
+maman|Bravo, Nino.
+narrateur|Le cube rouge reste en haut.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2151,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La pluie tape la vitre. Ça fait tic, tic, tic. Le radiateur est chaud. Le canapé a une couverture bleue. Une tour de cubes attend sur le tapis. Un cube rouge. Un cube vert. Nino, tu entends la pluie ? Oui. Tic, tic. Le radiateur est chaud. Mes mains aussi. En ce moment, Nino est au salon. Il touche un cube rouge. Son nez chatouille. Atchoum. Ton nez chatouille ? Oui, maman. Maman ouvre la boîte près du canapé. Maman tend un mouchoir. Prends un mouchoir. Nino prend un mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum, tout doux. Le nez est plus libre. Je respire. Mouchoir, puis poubelle. Nino va vers la poubelle. Il met le mouchoir dedans. La poubelle fait un petit bruit. Bravo. Tu as jeté le mouchoir. C'est du bon travail. Nino va au lavabo. Il se lave les mains. L'eau est tiède. Tu as fini de laver tes mains ? Oui, maman. Nino revient près des cubes. La tour attend encore. On pose le cube rouge ? Oui. Tout doux. Le cube rouge tient. La pluie tape encore. Tic, tic. Ton nez est calme, maintenant. Je respire mieux. Parce que tu as pris un mouchoir. Puis la poubelle. Mouchoir, poubelle. Oui. Bravo, Nino. Nino pose le cube vert. La tour est plus haute. Elle tient, la tour. Le rouge, puis le vert. Tu as les mains propres. Le radiateur ronronne tout bas. La couverture bleue glisse un peu. On la remet ? Oui. Elle est douce. Nino tire la couverture. Le canapé est chaud près du radiateur. La pluie continue. Tic, tic, tic. Et ton nez ? Calme. Mouchoir, poubelle. Bravo. C'est du bon travail.</t>
+          <t>La pluie tape la vitre. Ça fait tic, tic, tic. Le radiateur est chaud. Le canapé a une couverture bleue. Une tour de cubes attend sur le tapis. Un cube rouge. Un cube vert. Nino, tu entends la pluie ? Oui. Tic, tic. Le radiateur est chaud. Mes mains aussi. En ce moment, Nino est au salon. Il touche un cube rouge. Son nez chatouille. Atchoum. Ton nez chatouille ? Oui, maman. Maman ouvre la boîte près du canapé. Maman tend un mouchoir. Prends un mouchoir. Nino prend un mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum, tout doux. Le nez est plus libre. Je respire. Mouchoir, puis poubelle. Nino va vers la poubelle. Il met le mouchoir dedans. La poubelle fait un petit bruit. Bravo. Tu as jeté le mouchoir. Nino va au lavabo. Il se lave les mains. L'eau est tiède. Tu as fini de laver tes mains ? Oui, maman. Nino revient près des cubes. La tour attend encore. On pose le cube rouge ? Oui. Tout doux. Le cube rouge tient. La pluie tape encore. Tic, tic. Ton nez est calme, maintenant. Je respire mieux. Parce que tu as pris un mouchoir. Puis la poubelle. Mouchoir, poubelle. Oui. Bravo, Nino. Nino pose le cube vert. La tour est plus haute. Elle tient, la tour. Le rouge, puis le vert. Tu as les mains propres. Le radiateur ronronne tout bas. La couverture bleue glisse un peu. On la remet ? Oui. Elle est douce. Nino tire la couverture. Le canapé est chaud près du radiateur. La pluie continue. Tic, tic, tic. Et ton nez ? Calme. Mouchoir, poubelle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo est dans le salon. Son nez chatouille. Maman est près du canapé. Maman tend un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Hugo prend un mouchoir. Il se mouche. Atchoum, tout doux. Le nez est plus libre. Hugo va jeter le mouchoir. Il le met dans la poubelle. Maman dit : mouchoir, puis poubelle. Hugo va au lavabo. Il se lave les mains. Il revient. Maman sourit. Hugo respire mieux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pluie tape la vitre. Ça fait tic, tic, tic. Le radiateur est chaud. Le canapé a une couverture bleue. Une tour de cubes attend sur le tapis. Un cube rouge. Un cube vert. Nino, tu entends la pluie ? Oui. Tic, tic. Le radiateur est chaud. Mes mains aussi. En ce moment, Nino est au salon. Il touche un cube rouge. Son nez chatouille. Atchoum. Ton nez chatouille ? Oui, maman. Maman ouvre la boîte près du canapé. Maman tend un mouchoir. Prends un mouchoir. Nino prend un mouchoir. Le papier est doux. Il se mouche, tout doux. Atchoum, tout doux. Le nez est plus libre. Je respire. Mouchoir, puis poubelle. Nino va vers la poubelle. Il met le mouchoir dedans. La poubelle fait un petit bruit. Bravo. Tu as jeté le mouchoir. Nino va au lavabo. Il se lave les mains. L'eau est tiède. Tu as fini de laver tes mains ? Oui, maman. Nino revient près des cubes. La tour attend encore. On pose le cube rouge ? Oui. Tout doux. Le cube rouge tient. La pluie tape encore. Tic, tic. Ton nez est calme, maintenant. Je respire mieux. Parce que tu as pris un mouchoir. Puis la poubelle. Mouchoir, poubelle. Oui. Bravo, Nino. Nino pose le cube vert. La tour est plus haute. Elle tient, la tour. Le rouge, puis le vert. Tu as les mains propres. Le radiateur ronronne tout bas. La couverture bleue glisse un peu. On la remet ? Oui. Elle est douce. Nino tire la couverture. Le canapé est chaud près du radiateur. La pluie continue. Tic, tic, tic. Et ton nez ? Calme. Mouchoir, poubelle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1354,7 +1354,6 @@
 narrateur|Il met le mouchoir dedans.
 narrateur|La poubelle fait un petit bruit.
 maman|Bravo. Tu as jeté le mouchoir.
-maman|C'est du bon travail.
 narrateur|Nino va au lavabo.
 narrateur|Il se lave les mains.
 narrateur|L'eau est tiède.
@@ -1387,8 +1386,7 @@
 maman|La pluie continue.
 enfant-m|Tic, tic, tic.
 maman|Et ton nez ?
-enfant-m|Calme. Mouchoir, poubelle.
-maman|Bravo. C'est du bon travail.</t>
+enfant-m|Calme. Mouchoir, poubelle.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1425,7 +1423,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo se mouche. Que prend-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino se mouche. Que prend-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1604,12 +1602,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. Bravo. C'est du bon travail. La tour de cubes tient encore.</t>
+          <t>Nino a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. La tour de cubes tient encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo a pris un &lt;emphasis level="moderate"&gt;mouchoir&lt;/emphasis&gt;. Il s'est mouché. Il a jeté le mouchoir à la poubelle.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a pris un mouchoir. Il s'est mouché. Il a jeté le mouchoir à la poubelle. Tu as pris un mouchoir ? Oui. Puis poubelle. La tour de cubes tient encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1753,7 +1751,6 @@
 narrateur|Il a jeté le mouchoir à la poubelle.
 maman|Tu as pris un mouchoir ?
 enfant-m|Oui. Puis poubelle.
-maman|Bravo. C'est du bon travail.
 narrateur|La tour de cubes tient encore.</t>
         </is>
       </c>
@@ -1786,7 +1783,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo s'assoit près de maman. Son nez est calme. Il dit merci.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino s'assoit près de maman. La couverture bleue est douce. Merci, maman. Ton nez est calme. La pluie tape plus loin. Tic, tout doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,12 +1946,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Mouchoir, puis poubelle. Bravo, Nino. Le cube rouge reste en haut. L'histoire est finie.</t>
+          <t>Mouchoir, puis poubelle. Bravo, Nino. Le cube rouge reste en haut.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Mouchoir, puis poubelle. Bravo, Nino. Le cube rouge reste en haut.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2091,8 +2088,7 @@
         <is>
           <t>enfant-m|Mouchoir, puis poubelle.
 maman|Bravo, Nino.
-narrateur|Le cube rouge reste en haut.
-narrateur|L'histoire est finie.</t>
+narrateur|Le cube rouge reste en haut.</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2158,6 +2154,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
+++ b/stories/arbres/ATOM-SAN.HYG.003-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, pluie à la fenêtre, tour de cubes</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
